--- a/assets/docs/03_Expense_Invoice_Tracker.xlsx
+++ b/assets/docs/03_Expense_Invoice_Tracker.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="₱#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,10 +33,7 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -47,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F1A12"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,9 +63,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,249 +437,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Reference #</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Client/Vendor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Payment Status</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Payment Status</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>INV-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INV-001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Santos Events</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Design Service</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Monthly admin support</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Fictional amount</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INV-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Production coordination</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Follow up before due date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EXP-001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Office Supply Co.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Business storage</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Receipt filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EXP-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Office Supplies</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Printing and folders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Receipt filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EXP-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INV-002</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DC Marketing</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Admin Support</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Online Service</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Productivity tool</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EXP-002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Internet Provider</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Review renewal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
-  <dataValidations count="2">
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Revenue,Expense"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Paid,Pending,Overdue"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -689,62 +730,79 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Formula / Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUMIF(Transactions!C:C,"Income",Transactions!F:F)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <f>SUMIF(Transactions!E2:E,"Revenue",Transactions!G2:G)</f>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUMIF(Transactions!C:C,"Expense",Transactions!F:F)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>SUMIF(Transactions!E2:E,"Expense",Transactions!G2:G)</f>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>B2-B3</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>B3-B4</f>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Outstanding Income</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUMIFS(Transactions!F:F,Transactions!C:C,"Income",Transactions!G:G,"Outstanding")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Outstanding Revenue</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>SUMIFS(Transactions!G2:G,Transactions!E2:E,"Revenue",Transactions!H2:H,"Pending")</f>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Pending Expenses</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMIFS(Transactions!F:F,Transactions!C:C,"Expense",Transactions!G:G,"Pending")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>